--- a/_data_list/users.xlsx
+++ b/_data_list/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Telegram_Project\OrangeFlow_Dev\_data_list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43DD7F16-1610-4F08-AF6C-187690CCFECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7100DAD-7410-414D-896E-D236D21ACD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{BB0F9CCB-0FBE-4AFF-BD3B-D4E64BAEDA77}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{BB0F9CCB-0FBE-4AFF-BD3B-D4E64BAEDA77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="38">
   <si>
     <t xml:space="preserve"> TELEGRAM_ID</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>Shuvo</t>
+  </si>
+  <si>
+    <t>Sabbir Ahmed Bappy</t>
   </si>
 </sst>
 </file>
@@ -940,7 +943,24 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C21" s="1"/>
+      <c r="A21">
+        <v>6534313772</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21">
+        <v>1322159543</v>
+      </c>
+      <c r="D21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C22" s="1"/>
